--- a/SAKHALIN_KP_2810.xlsx
+++ b/SAKHALIN_KP_2810.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Построчно" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -756,43 +756,63 @@
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>rost (ФОБОС ФБ39)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>письмо 28.10.2026 (отправитель «rost»)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>60504.68</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>133640</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0.5472562107153547</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>в наличии; без доставки; предложение действует 5 календарных дней; 100% аванс (отгрузка после авансового платежа)</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>выгодно 55%: 30,3 тыс. с НДС при НМЦ 66,8 тыс.; Универсал из нержавейки вместо Классик Ст20 — эквивалент, согласовать; реквизиты и № реестра запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>4550995.32</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>5476742.55</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0.1690324534243443</v>
-      </c>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>4611500</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>5610382.55</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0.1780417896815254</v>
+      </c>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,92 млн (было 3,06 — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="n"/>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
@@ -800,6 +820,20 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,98 млн (было 3,06 — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -813,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3043,8 +3077,79 @@
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
     </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>rost (ФОБОС ФБ39)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>письмо 28.10.2026 (отправитель «rost»)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровый полнопроходной Классик ФБ39.210.050.000-02 DN50 PN4МПа Ст20 -40...+160C кл.А У1 фланцевый 230мм</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровый фланцевый «УНИВЕРСАЛ» DN50 PN16-40 12Х18Н9ТЛ/УХЛ1 L=230, -60…+160, кл. А, ФБ39.210.050.700-00, ТУ 3742-005-63149772-2010</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>24797</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>30252.34</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>66820</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.5472562107153547</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>60504.68</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>133640</v>
+      </c>
+      <c r="P33" s="13" t="inlineStr">
+        <is>
+          <t>выгодно</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>в ТЗ «Классик ФБ39.210.050.000-02», Ст20, У1: предложен «Универсал» -700-00 из 12Х18Н9ТЛ, УХЛ1 — характеристики не хуже, но обозначение другое → эквивалент с описанием или попросить именно Классик -000-02; № реестра ПП 719 (ФОБОС)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q32"/>
+  <autoFilter ref="A1:Q33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/SAKHALIN_KP_2810.xlsx
+++ b/SAKHALIN_KP_2810.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Построчно" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -790,43 +790,63 @@
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ЛМЗ</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 3028 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1396624.28</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2229540</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0.3735818689056936</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>100% предоплата; счёт действует 3 банк. дня; отгрузка 3–5 банк. дней, самовывоз Семёнов; вес всего 6 208 кг; позиции лота 1 (30ч906бр, 30ч39р, 32ч1р) и варианты LT — не нужны</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>30ч6бр Ду50–250 для лота 2: маржа 21–38% даже с КОФ (ВФЗ); позиции лота 1 в счёте не нужны; ЛМЗ — окр. среда от −15 °С: сверить с климатом ТЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>4611500</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>5610382.55</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0.1780417896815254</v>
-      </c>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>6008124.28</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>7839922.55</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0.2336500467086884</v>
+      </c>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,98 млн (было 3,06 — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
@@ -834,6 +854,20 @@
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,82 млн (было 3,06; ЛМЗ 30ч6бр дороже прежней оценки на 0,17 млн — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -847,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3148,8 +3182,363 @@
         </is>
       </c>
     </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ЛМЗ</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 3028 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка чугунная с КОФ 30ч6бр Ду 50 Ру 10/16 1исп.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр DN50 (ЛМЗ)</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>2854</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>3481.88</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>6900</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0.4953797101449275</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>139275.2</v>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>276000</v>
+      </c>
+      <c r="P34" s="13" t="inlineStr">
+        <is>
+          <t>выгодно</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>без КОФ — фланцы докупить (ВФЗ); ТЗ «с КОФ 1исп.»; LT-вариант дешевле, но не по ТЗ — не брать без проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ЛМЗ</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 3028 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка чугунная с КОФ 30ч6бр Ду 100 Ру 10/16 1исп.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр DN100 (ЛМЗ)</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>6741</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>8224.02</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0.4328262068965517</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>230272.56</v>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>406000</v>
+      </c>
+      <c r="P35" s="13" t="inlineStr">
+        <is>
+          <t>выгодно</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>без КОФ — фланцы докупить (ВФЗ); ТЗ «с КОФ 1исп.»; LT-вариант дешевле, но не по ТЗ — не брать без проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ЛМЗ</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 3028 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка чугунная с КОФ 30ч6бр Ду 150 Ру 10/16 1исп.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр DN150 (ЛМЗ)</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>15789</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>19262.58</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>30600</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0.3705039215686275</v>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>250413.54</v>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>397800</v>
+      </c>
+      <c r="P36" s="13" t="inlineStr">
+        <is>
+          <t>выгодно</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>без КОФ — фланцы докупить (ВФЗ); ТЗ «с КОФ 1исп.»; LT-вариант дешевле, но не по ТЗ — не брать без проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ЛМЗ</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 3028 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка чугунная с КОФ 30ч6бр Ду 200 Ру 10 1исп.</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр DN200 (ЛМЗ)</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>31425</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>38338.5</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>57500</v>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>0.3332434782608695</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>613416</v>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>920000</v>
+      </c>
+      <c r="P37" s="13" t="inlineStr">
+        <is>
+          <t>выгодно</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>без КОФ — фланцы докупить (ВФЗ); ТЗ «с КОФ 1исп.»; LT-вариант дешевле, но не по ТЗ — не брать без проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ЛМЗ</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 3028 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка чугунная с КОФ 30ч6бр Ду 250 Ру 10 1исп.</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр DN250 (ЛМЗ)</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>44603</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>54415.66</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>76580</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>0.2894272656045965</v>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>163246.98</v>
+      </c>
+      <c r="O38" s="6" t="n">
+        <v>229740</v>
+      </c>
+      <c r="P38" s="13" t="inlineStr">
+        <is>
+          <t>выгодно</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>без КОФ — фланцы докупить (ВФЗ); ТЗ «с КОФ 1исп.»; LT-вариант дешевле, но не по ТЗ — не брать без проверки</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q33"/>
+  <autoFilter ref="A1:Q38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/SAKHALIN_KP_2810.xlsx
+++ b/SAKHALIN_KP_2810.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Построчно" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -824,50 +824,118 @@
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ярдос</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>КП № 7852-К/26 от 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>505636.3199999999</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>600400</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.1578342438374418</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>100% предоплата; изготовление 30 кал. дн.; самовывоз Химки; гарантия 24/36 мес.; КП 30 дней; общепромышленное исполнение, ХЛ1</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>6 позиций ЗАРД/ЗАРДП — точно по ТЗ, маржа 14–20%; № реестра запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Гималаи</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 2104 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>95599.2</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.1614105263157894</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>100% предоплата; 30 кал. дн.; доставка до терминала Южно-Сахалинска за счёт поставщика; гарантия 18 мес.; счёт 30 дней</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>КШ250.8Д1 ×6 — точно по ТЗ, маржа 16%, доставка до Ю-Сахалинска включена</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>6008124.28</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>7839922.55</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0.2336500467086884</v>
-      </c>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,82 млн (было 3,06; ЛМЗ 30ч6бр дороже прежней оценки на 0,17 млн — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>6609359.8</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>8554322.550000001</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0.2273660758793811</v>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="9" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,88 млн (было 3,06; ЛМЗ 30ч6бр дороже прежней оценки на 0,17 млн — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -881,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3537,8 +3605,505 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Ярдос</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>КП № 7852-К/26 от 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровой запорный разборный фланцевый  (исполнение B по ГОСТ 33259-2015) из стали 14Х17Н2, в несейсмостойком исполнении С0, диаметр проходного сечения 29 мм, ЗАРД 032.016.21-01Р DN 32 PN 16 с ручным управлением</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>ЗАРД 032.016.21-01Р DN32 PN16</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>10418</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>12709.96</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>0.1526693333333334</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>25419.92</v>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="P39" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>обозначение совпадает с ТЗ дословно; № реестра ПП 719 запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Ярдос</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>КП № 7852-К/26 от 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровой запорный разборный полнопроходной  штуцерно-ниппельный из стали 14Х17Н2, в несейсмостойком исполнении С0, диаметр проходного сечения 10 мм, ЗАРДП 010.080.30-01Р DN 10 PN 80 с ручным управлением</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>ЗАРДП 010.080.30-01Р DN10 PN80</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>5420</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>6612.4</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>7860</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>0.1587277353689568</v>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>13224.8</v>
+      </c>
+      <c r="O40" s="6" t="n">
+        <v>15720</v>
+      </c>
+      <c r="P40" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>обозначение совпадает с ТЗ дословно; № реестра ПП 719 запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Ярдос</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>КП № 7852-К/26 от 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровой запорный разборный полнопроходной фланцевый (исполнение E по ГОСТ 33259-2015) из стали 14Х17Н2, в несейсмостойком исполнении С0, диаметр проходного сечения 65 мм, ЗАРДП 065.063.22-01Р DN 65 PN 63 с ручным управлением</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>ЗАРДП 065.063.22-01Р DN65 PN63</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>148013</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>180575.86</v>
+      </c>
+      <c r="L41" s="6" t="n">
+        <v>214620</v>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>0.1586251980244153</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>361151.72</v>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>429240</v>
+      </c>
+      <c r="P41" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>обозначение совпадает с ТЗ дословно; № реестра ПП 719 запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Ярдос</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>КП № 7852-К/26 от 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровой запорный разборный фланцевый (исполнение B по ГОСТ 33259-2015) из стали 14Х17Н2, в несейсмостойком исполнении С0, диаметр проходного сечения 36 мм, ЗАРД 040.016.21-01Р DN 40 PN 16 с ручным управлением</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>ЗАРД 040.016.21-01Р DN40 PN16</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>15669</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>19116.18</v>
+      </c>
+      <c r="L42" s="6" t="n">
+        <v>22720</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>0.158618838028169</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>38232.36</v>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>45440</v>
+      </c>
+      <c r="P42" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>обозначение совпадает с ТЗ дословно; № реестра ПП 719 запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Ярдос</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>КП № 7852-К/26 от 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровой запорный разборный фланцевый (исполнение B по ГОСТ 33259-2015) из стали 14Х17Н2, в несейсмостойком исполнении С0, диаметр проходного сечения 17 мм, ЗАРД 020.016.21-01Р DN 20 PN 16 с ручным управлением</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>ЗАРД 020.016.21-01Р DN20 PN16</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>7233</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>8824.26</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>0.1977945454545454</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>17648.52</v>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="P43" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>обозначение совпадает с ТЗ дословно; № реестра ПП 719 запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Ярдос</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>КП № 7852-К/26 от 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровой запорный разборный полнопроходной фланцевый (исполнение F по ГОСТ 33259-2015) из стали 12Х18Н10Т, в несейсмостойком исполнении С0, диаметр проходного сечения 25 мм, ЗАРДП 025.160.23-02Р DN 25 PN 160 с ручным управлением</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>ЗАРДП 025.160.23-02Р DN25 PN160</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>20475</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>24979.5</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>0.1386379310344827</v>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>49959</v>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>58000</v>
+      </c>
+      <c r="P44" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>обозначение совпадает с ТЗ дословно; № реестра ПП 719 запросить</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Гималаи</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Счёт № 2104 от 28.10.2026</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 2</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровый мнометрический КШ250.8Д1-Н23Б1ГН Кран шаровый мнометрический КШ250.8Д1-Н23Б1ГН</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровой манометрический КШ250.8Д1-Н23Б1ГН с приварным сбросным клапаном, PN25 МПа, DN8, нерж., AISI316</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>13060</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>15933.2</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>0.1614105263157896</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>95599.2</v>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>114000</v>
+      </c>
+      <c r="P45" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>обозначение как в ТЗ; доставка до Южно-Сахалинска включена</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q38"/>
+  <autoFilter ref="A1:Q45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/SAKHALIN_KP_2810.xlsx
+++ b/SAKHALIN_KP_2810.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Построчно" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Построчно'!$A$1:$Q$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,43 +892,63 @@
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ТД АДЛ</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>КП № УТД000114530 от 30.10.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>251752.2582</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>273040</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0.07796565265162614</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>100% предоплата; самовывоз Лыткарино; действует 2 дня; в КП 16 строк на 1,85 млн с НДС — для лота 2 нужны только 4 (ЗПВС 100/150 MN, Гранлок RD12 DN100/150)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>лот 2: ЗПВС Ду100/150 — 15%; Гранлок шаровой DN150 — 6%, DN100 — минус 2% (торг); остальные 12 строк КП — лот 1, не нужны</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>6609359.8</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>8554322.550000001</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>0.2273660758793811</v>
-      </c>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>6861112.0582</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>8827362.550000001</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0.2227449570200332</v>
+      </c>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,88 млн (было 3,06; ЛМЗ 30ч6бр дороже прежней оценки на 0,17 млн — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="n"/>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
@@ -936,6 +956,20 @@
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Влияние на лоты (снижение 10%, УСН): лот 2 (11202) прибыль ≈ 2,84 млн (было 3,06; ЛМЗ 30ч6бр дороже прежней оценки на 0,17 млн — МЭОФ-1600 96К по КП 172 тыс. против оценки 55 тыс.); лот 1 (11201) ≈ −0,38 млн (АРМАТЭК поз. 38).</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -949,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4102,8 +4136,292 @@
         </is>
       </c>
     </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ТД АДЛ</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>КП № УТД000114530 от 30.10.2026</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ® Затвор Поворотный Дисковый ЗПВС - FL(w)-3-100-MN-Е, Ду100, Ру16, межфланцевый, рукоятка, корпус - GG25, диск - GGG40, седло - EPDM, Траб=-15...+95°С</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-100-MN-Е Ду100</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>6384.62</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>7789.2364</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>9180</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>0.151499302832244</v>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>23367.7092</v>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>27540</v>
+      </c>
+      <c r="P46" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>точно по ТЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ТД АДЛ</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>КП № УТД000114530 от 30.10.2026</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ® Затвор Поворотный Дисковый ЗПВС - FL(w)-3-150-MN-Е, Ду150, Ру16, межфланцевый, рукоятка, корпус - GG25, диск - GGG40, седло - EPDM, Траб=-15...+95С</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>ГРАНВЭЛ ЗПВС FL(w)-3-150-MN-Е Ду150</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>9628.799999999999</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>11747.136</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>13850</v>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>0.1518313357400723</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>58735.67999999999</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>69250</v>
+      </c>
+      <c r="P47" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>точно по ТЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ТД АДЛ</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>КП № УТД000114530 от 30.10.2026</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Клапан обратный чугун шаровой фланцевый Ду 150 Ру16</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>ГРАНЛОК клапан обратный шаровой RD12.02.150.16.Ф/Ф DN150 (Тмакс 70°С)</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>30565.07</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>37289.3854</v>
+      </c>
+      <c r="L48" s="6" t="n">
+        <v>39830</v>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>0.06378645744413758</v>
+      </c>
+      <c r="N48" s="6" t="n">
+        <v>111868.1562</v>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>119490</v>
+      </c>
+      <c r="P48" s="14" t="inlineStr">
+        <is>
+          <t>торг / тонко</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>маржа 6% — торг</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ТД АДЛ</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>КП № УТД000114530 от 30.10.2026</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>ПАРТИЯ № 1</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Клапан обратный чугун шаровой фланцевый Ду 100 Ру16</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>ГРАНЛОК клапан обратный шаровой RD12.02.100.16.Ф/Ф DN100 (Тмакс 70°С)</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>15787.08</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>без НДС</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>19260.2376</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>18920</v>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>-0.01798295983086673</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>57780.7128</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>56760</v>
+      </c>
+      <c r="P49" s="16" t="inlineStr">
+        <is>
+          <t>не брать — дороже НМЦ</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>дороже НМЦ на 2% — торг или другой поставщик</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q45"/>
+  <autoFilter ref="A1:Q49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
